--- a/stats for com eng/excel files/Ch08-02.xlsx
+++ b/stats for com eng/excel files/Ch08-02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\OneDrive\2023-2024_3\2024-EGCI305\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/excel files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{46964FD7-2050-48EA-B290-E7C43D14FABB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F233B20-6B9F-4881-97F7-BFEC1523972C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3A03F1-9F10-C649-9E29-6862A0E7F24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12580" tabRatio="858" xr2:uid="{1702CB1B-5F51-4566-B5AE-3AF08FAEDD34}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="11040" tabRatio="858" activeTab="5" xr2:uid="{1702CB1B-5F51-4566-B5AE-3AF08FAEDD34}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -30,10 +30,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
   <si>
     <t>Sample</t>
   </si>
@@ -259,6 +259,12 @@
   <si>
     <t>Moving Average (4)</t>
   </si>
+  <si>
+    <t>no negative num for LCL so 0 is the number we will use</t>
+  </si>
+  <si>
+    <t>Moving Average (6)</t>
+  </si>
 </sst>
 </file>
 
@@ -268,7 +274,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,8 +337,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,8 +370,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="darkUp">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FF305496"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -407,11 +426,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0070C0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0070C0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -477,6 +507,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -707,64 +744,64 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>99.095000000000013</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -810,64 +847,64 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>105.9818980963046</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -913,64 +950,64 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>92.208101903695422</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1141,6 +1178,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1148,7 +1186,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1290,6 +1327,63 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
+                <c:pt idx="1">
+                  <c:v>7.2000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.10000000000000853</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.5999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.2999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.2999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9000000000000057</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.2000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.5999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.3999999999999915</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.6999999999999886</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.4000000000000057</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.29999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.5999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.1000000000000085</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.2000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.7999999999999972</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1334,61 +1428,61 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>2.5894736842105259</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1434,61 +1528,61 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>8.4598105263157883</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1759,6 +1853,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1766,7 +1861,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2012,64 +2106,64 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2115,64 +2209,64 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>3.2970562748477139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2446,6 +2540,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2453,7 +2548,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2603,6 +2697,66 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.2000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.9000000000000057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.2999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.29999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.2000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.79999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.8999999999999915</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.29999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.70000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.7000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-9.9999999999994316E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.9000000000000057</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2741,6 +2895,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2748,7 +2903,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2992,6 +3146,57 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
+                <c:pt idx="3">
+                  <c:v>98.375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>98.375</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>99.3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>99.474999999999994</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>99.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>98.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>98.699999999999989</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>99.274999999999991</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>99.524999999999991</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>99.799999999999983</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>99.875</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>98.800000000000011</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>98.3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>98.100000000000009</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>98.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>98.899999999999991</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99.974999999999994</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3161,6 +3366,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3168,7 +3374,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6523,14 +6728,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6568,7 +6769,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6674,7 +6875,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6816,7 +7017,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6825,7 +7026,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A2B2DF1-4FAE-4791-9B60-90F49914F0C0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6835,14 +7036,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DFF0BF-6505-4DAF-8D0A-5C7D79BF4505}">
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.81640625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="15.81640625" style="2" customWidth="1"/>
-    <col min="4" max="9" width="7.81640625" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="15.83203125" style="2" customWidth="1"/>
+    <col min="4" max="9" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -6871,7 +7072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -6881,667 +7082,742 @@
       <c r="C2" s="6"/>
       <c r="D2" s="8">
         <f>$B$22</f>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E2" s="8">
         <f>$B$23</f>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F2" s="8">
         <f>$B$24</f>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4">
         <v>94.8</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="4">
+        <f>ABS(B3-B2)</f>
+        <v>7.2000000000000028</v>
+      </c>
       <c r="D3" s="8">
         <f t="shared" ref="D3:D21" si="0">$B$22</f>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E3" s="8">
         <f t="shared" ref="E3:E21" si="1">$B$23</f>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F3" s="8">
         <f t="shared" ref="F3:F21" si="2">$B$24</f>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G3" s="8">
         <f t="shared" ref="G3:G21" si="3">$C$22</f>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H3" s="8">
         <f t="shared" ref="H3:H21" si="4">$C$23</f>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I3" s="8">
         <f t="shared" ref="I3:I21" si="5">$C$24</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4">
         <v>98.3</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="4">
+        <f t="shared" ref="C4:C21" si="6">ABS(B4-B3)</f>
+        <v>3.5</v>
+      </c>
       <c r="D4" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E4" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F4" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G4" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I4" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4">
         <v>98.4</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="4">
+        <f t="shared" si="6"/>
+        <v>0.10000000000000853</v>
+      </c>
       <c r="D5" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E5" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F5" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I5" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="4">
         <v>102</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="4">
+        <f t="shared" si="6"/>
+        <v>3.5999999999999943</v>
+      </c>
       <c r="D6" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E6" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F6" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G6" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I6" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="4">
         <v>98.5</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="4">
+        <f t="shared" si="6"/>
+        <v>3.5</v>
+      </c>
       <c r="D7" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F7" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I7" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4">
         <v>99</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="4">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
       <c r="D8" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F8" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G8" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H8" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I8" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4">
         <v>97.7</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="4">
+        <f t="shared" si="6"/>
+        <v>1.2999999999999972</v>
+      </c>
       <c r="D9" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F9" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I9" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="4">
         <v>100</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="4">
+        <f t="shared" si="6"/>
+        <v>2.2999999999999972</v>
+      </c>
       <c r="D10" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E10" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F10" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G10" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H10" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I10" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="4">
         <v>98.1</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="4">
+        <f t="shared" si="6"/>
+        <v>1.9000000000000057</v>
+      </c>
       <c r="D11" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F11" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I11" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="4">
         <v>101.3</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="4">
+        <f t="shared" si="6"/>
+        <v>3.2000000000000028</v>
+      </c>
       <c r="D12" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E12" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F12" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H12" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I12" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="4">
         <v>98.7</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="4">
+        <f t="shared" si="6"/>
+        <v>2.5999999999999943</v>
+      </c>
       <c r="D13" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E13" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F13" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I13" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="4">
         <v>101.1</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="4">
+        <f t="shared" si="6"/>
+        <v>2.3999999999999915</v>
+      </c>
       <c r="D14" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E14" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F14" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G14" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H14" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I14" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="4">
         <v>98.4</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="4">
+        <f t="shared" si="6"/>
+        <v>2.6999999999999886</v>
+      </c>
       <c r="D15" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E15" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F15" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I15" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="4">
         <v>97</v>
       </c>
-      <c r="C16" s="4"/>
+      <c r="C16" s="4">
+        <f t="shared" si="6"/>
+        <v>1.4000000000000057</v>
+      </c>
       <c r="D16" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E16" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F16" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G16" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H16" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I16" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="4">
         <v>96.7</v>
       </c>
-      <c r="C17" s="4"/>
+      <c r="C17" s="4">
+        <f t="shared" si="6"/>
+        <v>0.29999999999999716</v>
+      </c>
       <c r="D17" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E17" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F17" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I17" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="4">
         <v>100.3</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="4">
+        <f t="shared" si="6"/>
+        <v>3.5999999999999943</v>
+      </c>
       <c r="D18" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E18" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F18" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G18" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H18" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I18" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="4">
         <v>101.4</v>
       </c>
-      <c r="C19" s="4"/>
+      <c r="C19" s="4">
+        <f t="shared" si="6"/>
+        <v>1.1000000000000085</v>
+      </c>
       <c r="D19" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E19" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F19" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I19" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="4">
         <v>97.2</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="4">
+        <f t="shared" si="6"/>
+        <v>4.2000000000000028</v>
+      </c>
       <c r="D20" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E20" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F20" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G20" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I20" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="4">
         <v>101</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="4">
+        <f t="shared" si="6"/>
+        <v>3.7999999999999972</v>
+      </c>
       <c r="D21" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99.095000000000013</v>
       </c>
       <c r="E21" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105.9818980963046</v>
       </c>
       <c r="F21" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>92.208101903695422</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5894736842105259</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4598105263157883</v>
       </c>
       <c r="I21" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-    </row>
-    <row r="23" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="14">
+        <f>AVERAGE(B2:B21)</f>
+        <v>99.095000000000013</v>
+      </c>
+      <c r="C22" s="14">
+        <f>AVERAGE(C3:C21)</f>
+        <v>2.5894736842105259</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-    </row>
-    <row r="24" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="14">
+        <f>B22+3*C22/1.128</f>
+        <v>105.9818980963046</v>
+      </c>
+      <c r="C23" s="14">
+        <f>3.267*C22</f>
+        <v>8.4598105263157883</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="B24" s="14">
+        <f>B22-3*C22/1.128</f>
+        <v>92.208101903695422</v>
+      </c>
+      <c r="C24" s="14">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7553,80 +7829,105 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D3FAE9-31C6-473F-AF03-C3FFCA4C167C}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.83203125" defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="13"/>
-    </row>
-    <row r="2" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="13">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="13"/>
-    </row>
-    <row r="3" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="13">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="13"/>
-    </row>
-    <row r="4" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="13">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="13"/>
-    </row>
-    <row r="6" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="13">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15"/>
-    </row>
-    <row r="8" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="15">
+        <f>(B1-B2)/(6*B4)</f>
+        <v>2.2222222222222223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="15"/>
-    </row>
-    <row r="10" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="15">
+        <f>MIN(B1-B3/(3*B4), (B3-B2)/(3*B4))</f>
+        <v>3.7777777777777777</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>0.66669999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="str">
         <f xml:space="preserve"> "  = P(Z &lt; (" &amp; B2 &amp; " - " &amp; B3 &amp; ")/" &amp; B4 &amp; ") "</f>
-        <v xml:space="preserve">  = P(Z &lt; ( - )/) </v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v xml:space="preserve">  = P(Z &lt; (90 - 107)/1.5) </v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="15"/>
-    </row>
-    <row r="14" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="15">
+        <f>_xlfn.NORM.S.DIST(-11.33, TRUE)</f>
+        <v>4.6602370591334567E-30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="str">
         <f xml:space="preserve"> "  = P(Z &gt; (" &amp; B1 &amp; " - " &amp; B3 &amp; ")/" &amp; B4 &amp; ") "</f>
-        <v xml:space="preserve">  = P(Z &gt; ( - )/) </v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v xml:space="preserve">  = P(Z &gt; (110 - 107)/1.5) </v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="15"/>
+      <c r="B16" s="15">
+        <f>1-_xlfn.NORM.S.DIST(2,TRUE)</f>
+        <v>2.2750131948179209E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7637,46 +7938,58 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D36AD84B-0A08-4BC9-A9B6-BE49F6A4D5D0}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.83203125" defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="20"/>
-    </row>
-    <row r="2" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="20"/>
-    </row>
-    <row r="3" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="20"/>
-    </row>
-    <row r="5" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="13"/>
-    </row>
-    <row r="6" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="13">
+        <f>B3+3*SQRT(B3*(1-B3)/B2)</f>
+        <v>0.54696938456699074</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="13">
         <f>B3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="13"/>
+      <c r="B7" s="13">
+        <f>B3-3*SQRT(B3*(1-B3)/B2)</f>
+        <v>0.25303061543300936</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7686,18 +7999,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B46F67-4662-47AA-B167-74DA3E73271F}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.83203125" defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="6" width="7.81640625" style="2" customWidth="1"/>
+    <col min="4" max="6" width="7.83203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="19" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" s="19" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>0</v>
       </c>
@@ -7717,7 +8030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -7730,18 +8043,18 @@
       </c>
       <c r="D3" s="24">
         <f>$C$23</f>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E3" s="24">
         <f>$B$26</f>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F3" s="24">
         <f>$C$27</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -7754,18 +8067,18 @@
       </c>
       <c r="D4" s="24">
         <f t="shared" ref="D4:D22" si="1">$C$23</f>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E4" s="24">
         <f t="shared" ref="E4:E22" si="2">$B$26</f>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F4" s="24">
         <f t="shared" ref="F4:F22" si="3">$C$27</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -7778,18 +8091,18 @@
       </c>
       <c r="D5" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E5" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F5" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -7802,18 +8115,18 @@
       </c>
       <c r="D6" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E6" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F6" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -7826,18 +8139,18 @@
       </c>
       <c r="D7" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E7" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F7" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -7850,18 +8163,18 @@
       </c>
       <c r="D8" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E8" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F8" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -7874,18 +8187,18 @@
       </c>
       <c r="D9" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E9" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F9" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -7898,18 +8211,18 @@
       </c>
       <c r="D10" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E10" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F10" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -7922,18 +8235,18 @@
       </c>
       <c r="D11" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E11" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F11" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -7946,18 +8259,18 @@
       </c>
       <c r="D12" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E12" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F12" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -7970,18 +8283,18 @@
       </c>
       <c r="D13" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E13" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F13" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -7994,18 +8307,18 @@
       </c>
       <c r="D14" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E14" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F14" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -8018,18 +8331,18 @@
       </c>
       <c r="D15" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E15" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F15" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -8042,18 +8355,18 @@
       </c>
       <c r="D16" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E16" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F16" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -8066,18 +8379,18 @@
       </c>
       <c r="D17" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E17" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F17" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -8090,18 +8403,18 @@
       </c>
       <c r="D18" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E18" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F18" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -8114,18 +8427,18 @@
       </c>
       <c r="D19" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E19" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F19" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -8138,18 +8451,18 @@
       </c>
       <c r="D20" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E20" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F20" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -8162,18 +8475,18 @@
       </c>
       <c r="D21" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E21" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F21" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -8186,42 +8499,61 @@
       </c>
       <c r="D22" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E22" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.2970562748477139</v>
       </c>
       <c r="F22" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="25" t="s">
         <v>3</v>
       </c>
       <c r="B23" s="26"/>
-      <c r="C23" s="14"/>
-    </row>
-    <row r="25" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="14">
+        <f>AVERAGE(C3:C22)</f>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="13"/>
-    </row>
-    <row r="26" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="13">
+        <f>5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="22"/>
-    </row>
-    <row r="27" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="22">
+        <f>C23+3*SQRT(C23/B25)</f>
+        <v>3.2970562748477139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="13"/>
+        <v>5</v>
+      </c>
+      <c r="B27" s="22">
+        <f>C23-3*SQRT(C23/B25)</f>
+        <v>-9.7056274847713953E-2</v>
+      </c>
+      <c r="C27" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8234,18 +8566,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B929E09-484C-41DF-BDF7-CF9B34D05CF8}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="18.81640625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.83203125" defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -8261,8 +8593,11 @@
       <c r="E2" s="12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F2" s="27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -8273,10 +8608,14 @@
         <f>B3-99</f>
         <v>3</v>
       </c>
-      <c r="D3" s="14"/>
+      <c r="D3" s="14">
+        <f>C3</f>
+        <v>3</v>
+      </c>
       <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -8287,10 +8626,14 @@
         <f t="shared" ref="C4:C22" si="0">B4-99</f>
         <v>-4.2000000000000028</v>
       </c>
-      <c r="D4" s="14"/>
+      <c r="D4" s="14">
+        <f>C4+D3</f>
+        <v>-1.2000000000000028</v>
+      </c>
       <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -8301,10 +8644,14 @@
         <f t="shared" si="0"/>
         <v>-0.70000000000000284</v>
       </c>
-      <c r="D5" s="14"/>
+      <c r="D5" s="14">
+        <f t="shared" ref="D5:D22" si="1">C5+D4</f>
+        <v>-1.9000000000000057</v>
+      </c>
       <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -8315,10 +8662,17 @@
         <f t="shared" si="0"/>
         <v>-0.59999999999999432</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D6" s="14">
+        <f t="shared" si="1"/>
+        <v>-2.5</v>
+      </c>
+      <c r="E6" s="4">
+        <f>AVERAGE(B3:B6)</f>
+        <v>98.375</v>
+      </c>
+      <c r="F6" s="29"/>
+    </row>
+    <row r="7" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -8329,10 +8683,17 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D7" s="14">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" ref="E7:E22" si="2">AVERAGE(B4:B7)</f>
+        <v>98.375</v>
+      </c>
+      <c r="F7" s="29"/>
+    </row>
+    <row r="8" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -8343,10 +8704,20 @@
         <f t="shared" si="0"/>
         <v>-0.5</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D8" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="2"/>
+        <v>99.3</v>
+      </c>
+      <c r="F8" s="28">
+        <f>AVERAGE(B3:B8)</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -8357,10 +8728,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D9" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="2"/>
+        <v>99.474999999999994</v>
+      </c>
+      <c r="F9" s="28">
+        <f t="shared" ref="F9:F22" si="3">AVERAGE(B4:B9)</f>
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -8371,10 +8752,20 @@
         <f t="shared" si="0"/>
         <v>-1.2999999999999972</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D10" s="14">
+        <f t="shared" si="1"/>
+        <v>-1.2999999999999972</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="2"/>
+        <v>99.3</v>
+      </c>
+      <c r="F10" s="28">
+        <f t="shared" si="3"/>
+        <v>98.983333333333334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -8385,10 +8776,20 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D11" s="14">
+        <f t="shared" si="1"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" si="2"/>
+        <v>98.8</v>
+      </c>
+      <c r="F11" s="28">
+        <f t="shared" si="3"/>
+        <v>99.266666666666652</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -8399,10 +8800,20 @@
         <f t="shared" si="0"/>
         <v>-0.90000000000000568</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D12" s="14">
+        <f t="shared" si="1"/>
+        <v>-1.2000000000000028</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="2"/>
+        <v>98.699999999999989</v>
+      </c>
+      <c r="F12" s="28">
+        <f t="shared" si="3"/>
+        <v>99.216666666666654</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -8413,10 +8824,20 @@
         <f t="shared" si="0"/>
         <v>2.2999999999999972</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D13" s="14">
+        <f t="shared" si="1"/>
+        <v>1.0999999999999943</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="2"/>
+        <v>99.274999999999991</v>
+      </c>
+      <c r="F13" s="28">
+        <f t="shared" si="3"/>
+        <v>99.09999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -8427,10 +8848,20 @@
         <f t="shared" si="0"/>
         <v>-0.29999999999999716</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D14" s="14">
+        <f t="shared" si="1"/>
+        <v>0.79999999999999716</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="2"/>
+        <v>99.524999999999991</v>
+      </c>
+      <c r="F14" s="28">
+        <f t="shared" si="3"/>
+        <v>99.133333333333326</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -8441,10 +8872,20 @@
         <f t="shared" si="0"/>
         <v>2.0999999999999943</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D15" s="14">
+        <f t="shared" si="1"/>
+        <v>2.8999999999999915</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="2"/>
+        <v>99.799999999999983</v>
+      </c>
+      <c r="F15" s="28">
+        <f t="shared" si="3"/>
+        <v>99.483333333333334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -8455,10 +8896,20 @@
         <f t="shared" si="0"/>
         <v>-0.59999999999999432</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D16" s="14">
+        <f t="shared" si="1"/>
+        <v>2.2999999999999972</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="2"/>
+        <v>99.875</v>
+      </c>
+      <c r="F16" s="28">
+        <f t="shared" si="3"/>
+        <v>99.59999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -8469,10 +8920,20 @@
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D17" s="14">
+        <f t="shared" si="1"/>
+        <v>0.29999999999999716</v>
+      </c>
+      <c r="E17" s="4">
+        <f t="shared" si="2"/>
+        <v>98.800000000000011</v>
+      </c>
+      <c r="F17" s="28">
+        <f t="shared" si="3"/>
+        <v>99.09999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -8483,10 +8944,20 @@
         <f t="shared" si="0"/>
         <v>-2.2999999999999972</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D18" s="14">
+        <f t="shared" si="1"/>
+        <v>-2</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="2"/>
+        <v>98.3</v>
+      </c>
+      <c r="F18" s="28">
+        <f t="shared" si="3"/>
+        <v>98.866666666666674</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -8497,10 +8968,20 @@
         <f t="shared" si="0"/>
         <v>1.2999999999999972</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D19" s="14">
+        <f t="shared" si="1"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" si="2"/>
+        <v>98.100000000000009</v>
+      </c>
+      <c r="F19" s="28">
+        <f t="shared" si="3"/>
+        <v>98.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -8511,10 +8992,20 @@
         <f t="shared" si="0"/>
         <v>2.4000000000000057</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D20" s="14">
+        <f t="shared" si="1"/>
+        <v>1.7000000000000028</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="2"/>
+        <v>98.85</v>
+      </c>
+      <c r="F20" s="28">
+        <f t="shared" si="3"/>
+        <v>99.149999999999991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -8525,10 +9016,20 @@
         <f t="shared" si="0"/>
         <v>-1.7999999999999972</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D21" s="14">
+        <f t="shared" si="1"/>
+        <v>-9.9999999999994316E-2</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" si="2"/>
+        <v>98.899999999999991</v>
+      </c>
+      <c r="F21" s="28">
+        <f t="shared" si="3"/>
+        <v>98.500000000000014</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -8539,10 +9040,20 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D22" s="14">
+        <f t="shared" si="1"/>
+        <v>1.9000000000000057</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="2"/>
+        <v>99.974999999999994</v>
+      </c>
+      <c r="F22" s="28">
+        <f t="shared" si="3"/>
+        <v>98.933333333333323</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
